--- a/paper/tables/final/Tabela_3_painel_A.xlsx
+++ b/paper/tables/final/Tabela_3_painel_A.xlsx
@@ -240,7 +240,7 @@
     <t>0,49</t>
   </si>
   <si>
-    <t>Fonte: Mais Retorno (relatórios PDF exportados; licença comercial).</t>
+    <t>Fonte: Mais Retorno (relatórios PDF exportados; uso acadêmico autorizado).</t>
   </si>
   <si>
     <t>Nota:  Excesso = CAGR da série − CAGR do CDI (em p.p.). Amplitude = max(excesso) − min(excesso) entre D0, D-6m e D-12m.</t>
